--- a/docs/data/hotspot-daily-2026-04-13.xlsx
+++ b/docs/data/hotspot-daily-2026-04-13.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全量数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精选话题" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="全量数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="精选话题" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全量数据'!$A$1:$W$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'精选话题'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全量数据'!$A$1:$W$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'精选话题'!$A$1:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -632,97 +632,25 @@
           <t>hackernews</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Ask HN: What Are You Working On? (April 2026)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.ycombinator.com/item?id=47741527</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Ask HN: What Are You Working On? (April ：问 HN：您在做什么？(April 2026) |黑客新闻 黑客新闻 新 |past |comments |ask |show |jobs |提交登录 询问 HN：您在做什么？</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Claude, Cursor</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>CodeBuddy</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>P2 观察中</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>**Ask HN: What Are You Working On? (April ** 是 AI 编程赛道产品 — 可以做 CodeBuddy vs Ask HN: What Are You Working On? (April  的横向对比：CodeBuddy 覆盖需求→设计→编码→测试全流程，IDE 原生集成而非浏览器插件</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>以 Ask HN: What Are You Working On? (April  引发的开发者效率讨论为切入点，写一篇 CodeBuddy 的实际使用案例：用 CodeBuddy 的 Agent 模式从零构建一个类似功能，展示 AI 编码的真实生产力。</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>「Ask HN: What Are You Working On? (April…」是 CodeBuddy 的同赛道竞品，适合做横向对比评测内容，突出 IDE 集成和中文支持的差异化优势。P1 本周发（讨论还在活跃期），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>david927</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.ycombinator.com/user?id=david927</t>
-        </is>
-      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -972,7 +900,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>markitdown：Python 工具 for converting files and office documents to Markdown</t>
+          <t>markitdown：用于将文件和 Office 文档转换为 Markdown 的 Python 工具。</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1412,7 +1340,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>andrej-karpathy-skills — AI 编程/代码辅助工具</t>
+          <t>andrej-karpathy-skills：一个单独的克劳德。md 文件来改进 Claude 代码行为，源自 Andrej Karpathy 对 LLM 编码陷阱的观察。</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1618,23 +1546,75 @@
           <t>36kr</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>众擎机器人旗下公司、锋物科技在北京成立机器人公司</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/newsflashes/3764715816370691</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>众擎机器人旗下公司、锋物科技在北京成立机器人公司-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 众擎机器人旗下公司、锋物科技在北京成立机器人公司 爱企查App显示，近期，北京锋物机器人有限公司成立，法定代表人为李明远，注册资本500万元人民币，经营范围包括工业机器人销售、智能机器人的研发、智能机器人销售、工业机器人制造、人工智能双创服务平台等。 股东…</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>P2 观察中</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>「众擎机器人旗下公司、锋物科技在北京成立机器人公司」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="2" t="inlineStr"/>
@@ -1647,27 +1627,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>🐱 产品猎人</t>
+          <t>🚀 创投快讯</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>producthunt</t>
+          <t>36kr</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Nicelydone MCP</t>
+          <t>橡鹿机器人启动1亿生态扶持计划</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.producthunt.com/products/nicely-done</t>
+          <t>https://36kr.com/newsflashes/3764742260195846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Nicelydone MCP：设计 context for AI Agent</t>
+          <t>橡鹿机器人启动1亿生态扶持计划-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 橡鹿机器人启动1亿生态扶持计划 4月13日，橡鹿机器人正式启动1亿生态扶持计划。 面向中餐产业链上下游伙伴，联合投资机构、行业协会及餐饮品牌，共同打造全球最大的中餐机器人产业生态圈。</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1682,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1692,7 +1672,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1702,11 +1682,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>MCP</t>
-        </is>
-      </c>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
@@ -1725,14 +1701,10 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>「Nicelydone MCP」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>fmerian</t>
-        </is>
-      </c>
+          <t>「橡鹿机器人启动1亿生态扶持计划」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="inlineStr"/>
     </row>
@@ -1744,27 +1716,27 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>🐱 产品猎人</t>
+          <t>🚀 创投快讯</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>producthunt</t>
+          <t>36kr</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Layered</t>
+          <t>AI潮玩品牌“MOMOTOY”完成数千万元融资</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.producthunt.com/products/layered-2</t>
+          <t>https://36kr.com/newsflashes/3764740131308297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Layered：Turn your selfies into a personal AI stylist</t>
+          <t>AI潮玩品牌“MOMOTOY”完成数千万元融资-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 AI潮玩品牌“MOMOTOY”完成数千万元融资 AI潮玩品牌“MOMOTOY”已完成数千万元融资，由翼朴基金投资，投后估值2. 品牌负责人透露，本轮融资资金，会重点投向AI技术迭代、高端产品矩阵落地、全球渠道拓展及核心商圈旗舰店铺设四大核心领域。</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1761,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1818,14 +1790,10 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>「Layered」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>Vadim Drobinin</t>
-        </is>
-      </c>
+          <t>「AI潮玩品牌“MOMOTOY”完成数千万元融资」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr"/>
       <c r="W13" s="2" t="inlineStr"/>
     </row>
@@ -1837,27 +1805,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>🐱 产品猎人</t>
+          <t>🚀 创投快讯</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>producthunt</t>
+          <t>36kr</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ClarifierAI for IOS</t>
+          <t>恒指午间休盘跌1.18%，恒生科技指数跌0.98%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.producthunt.com/products/clarifierai-rewrite-text-2</t>
+          <t>https://36kr.com/newsflashes/3764731386708487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>ClarifierAI for IOS：使用 AI 编写和翻译消息的速度提高 10 倍</t>
+          <t>恒指午间休盘跌1.18%，恒生科技指数跌0.98%: 恒指午间休盘跌1. 18%，恒生科技指数跌0. 98%-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 恒指午间休盘跌1. 18%，恒生科技指数跌0.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1872,7 +1840,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1882,7 +1850,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1911,14 +1879,10 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>「ClarifierAI for IOS」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>Daniil Park</t>
-        </is>
-      </c>
+          <t>「恒指午间休盘跌1.18%，恒生科技指数跌0.98%」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr"/>
       <c r="W14" s="2" t="inlineStr"/>
     </row>
@@ -1930,27 +1894,27 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>🐱 产品猎人</t>
+          <t>🚀 创投快讯</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>producthunt</t>
+          <t>36kr</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Interactive Simulations in Gemini</t>
+          <t>半日主力资金加仓电子板块，抛售医药生物板块</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.producthunt.com/products/gemini-6</t>
+          <t>https://36kr.com/newsflashes/3764706982281737</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Interactive Simulations in Gemini：Gemini now lets you play with the concepts you ask about</t>
+          <t>半日主力资金加仓电子板块，抛售医药生物板块-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 半日主力资金加仓电子板块，抛售医药生物板块 主力资金早间净流入电子、计算机等板块，净流出医药生物、传媒等板块。 具体到个股来看，胜宏科技、中材科技、浪潮信息获净流入14. 93亿元、11. 83亿元、10.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1965,7 +1929,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1975,7 +1939,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1983,11 +1947,7 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Gemini</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -2008,125 +1968,101 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>「Interactive Simulations in Gemini」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>Zac Zuo</t>
-        </is>
-      </c>
+          <t>「半日主力资金加仓电子板块，抛售医药生物板块」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr"/>
       <c r="W15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>🤓 极客社区</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>v2ex</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>咸鱼 codex 模型注水，用千问 0.6b 代替 codex5.4</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1205234</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>咸鱼 codex 模型注水，用千问 0.6b 代替 codex5.4: []( https://i. com/inSQwPb.</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>🚀 创投快讯</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>36kr</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>A股三大指数午间休盘涨跌不一，玻璃纤维概念走强</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/newsflashes/3764701370876423</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>A股三大指数午间休盘涨跌不一，玻璃纤维概念走强-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 A股三大指数午间休盘涨跌不一，玻璃纤维概念走强 A股三大指数午间休盘涨跌不一，沪指跌0. 17%，深成指涨0. 19%，创业板指涨0. 39%；玻璃纤维、锂矿、CPO概念领涨，宏和科技、西藏城投涨停，太辰光涨超5%，海运、能源设备、保险板块跌幅居前，中远海能…</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT, Claude, 通义千问</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>Hunyuan</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>P1 本周发</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t>「咸鱼模型注水用千」话题与 Hunyuan 存在场景关联，但关联度中等，建议结合具体讨论内容判断是否植入</t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>以「咸鱼模型注水用千」话题为引子，从社区讨论中提炼出一个具体的技术痛点，用 Hunyuan 的能力来给出解决方案。</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>「咸鱼 codex 模型注水，用千问 0.6b 代替 codex5.4」可从 Hunyuan 的使用场景切入参与讨论。P1 本周发（讨论还在活跃期），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>bingoso</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/member/bingoso</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>P2 观察中</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>「A股三大指数午间休盘涨跌不一，玻璃纤维概念走强」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2136,27 +2072,27 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>🤓 极客社区</t>
+          <t>🚀 创投快讯</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>v2ex</t>
+          <t>36kr</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>[合肥] 初级小程序全栈工程师</t>
+          <t>多晶硅主力合约涨幅扩大至6%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1205233</t>
+          <t>https://36kr.com/newsflashes/3764695334683398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>开发的⼩程序不是很复杂，但是前端后端还有运维都会接触⼀些（前端侧重的多⼀些） 我们希望你： - 了解 UniApp Vue 开发 - 有过独自开发全栈应用的经历（不要求多复杂） - 了解某个后端框架，⽐如 ThinkPHP ，SpringBoot ，Django 等 - 有过 Linux 和 Nginx 操作和配置经验 - 了解一些 Python 和 Bash - 对于从前端到后端再到数据库之间…</t>
+          <t>多晶硅主力合约涨幅扩大至6%-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 多晶硅主力合约涨幅扩大至6% 多晶硅主力合约持续走高，涨幅扩大至6%，现报33875元/吨。</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2171,40 +2107,28 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>ChatGPT, Claude</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Go, Python, Vue</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>CodeBuddy</t>
-        </is>
-      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -2212,29 +2136,21 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>「初级小程序全栈工」涉及开发者效率话题 — CodeBuddy 提供从需求规划到代码发布的一站式 AI 编码体验，可以作为开发效率提升的具体工具推荐</t>
+          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>借「初级小程序全栈工」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（开发的⼩程序不是很复杂，但是前端后端还有运维都会接触⼀些（前端侧重的多⼀些） 我们希望你： - 了解 UniApp Vue 开发 - 有过独自开发全栈应用的经…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
+          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>「[合肥] 初级小程序全栈工程师」讨论 AI 编程工具话题，可以自然切入 CodeBuddy 做产品推荐。P1 本周发（讨论还在活跃期），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>yujiehan2002</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/member/yujiehan2002</t>
-        </is>
-      </c>
+          <t>「多晶硅主力合约涨幅扩大至6%」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
       <c r="W17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2245,27 +2161,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>🤓 极客社区</t>
+          <t>🚀 创投快讯</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>v2ex</t>
+          <t>36kr</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Gemini 访问不了，换了台湾家宽也不行，用什么梯子能访问啊？</t>
+          <t>玉禾田：未设立垃圾焚烧发电厂</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1205253</t>
+          <t>https://36kr.com/newsflashes/3764693179859463</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Gemini 访问不了，换了台湾家宽也不行，用什么梯子能访问啊？: 确实是 IP 的问题，无痕模式中在未登录的状态发送消息也发不出去，已经换上了家宽了，有人知道 Gemini 是怎么鉴定 IP 的吗？ 我已经连续很多天用不了 Gemini 了，很痛苦。</t>
+          <t>玉禾田：未设立垃圾焚烧发电厂-36氪 36氪Auto 36氪出海 36氪研究院 36氪 36氪财经 AI 自助报道 城市 玉禾田：未设立垃圾焚烧发电厂 玉禾田在互动平台表示，公司未设立垃圾焚烧发电厂。</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2275,39 +2191,31 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>ChatGPT, Claude, Gemini</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
@@ -2327,19 +2235,11 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>「Gemini 访问不了，换了台湾家宽也不行，用什么梯子能访问啊？」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>walterggg</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/member/walterggg</t>
-        </is>
-      </c>
+          <t>「玉禾田：未设立垃圾焚烧发电厂」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -2350,27 +2250,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>🤓 极客社区</t>
+          <t>🐱 产品猎人</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>v2ex</t>
+          <t>producthunt</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026 年， V 友们认为最省内存的浏览器是哪个呢？你目前在用的是什么浏览器？</t>
+          <t>Nicelydone MCP</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1205227</t>
+          <t>https://www.producthunt.com/products/nicely-done</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026 年， V 友们认为最省内存的浏览器是哪个呢？你目前在用的是什么浏览器？: 2026 年， V 友们认为最省内存的浏览器是哪个呢？ 你目前在用的是什么浏览器？ - V2EX 首页 注册 登录 V2EX = way to explore V2EX 是一个关于分享和探索的地方 现在注册 已注册用户请 登录 V2EX › 浏览器 2026 年， V 友们认为最省内存的浏览器是哪个呢？ 你目前在…</t>
+          <t>Nicelydone MCP：AI 代理的设计环境</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2380,32 +2280,36 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
@@ -2424,19 +2328,15 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>「2026 年， V 友们认为最省内存的浏览器是哪个呢？你目前在用的是什么浏览器？」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
+          <t>「Nicelydone MCP」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>Astralume</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/member/Astralume</t>
-        </is>
-      </c>
+          <t>fmerian</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2447,52 +2347,52 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>🤓 极客社区</t>
+          <t>🐱 产品猎人</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>v2ex</t>
+          <t>producthunt</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>[ Codex 中转站 | 纯 plus 号池] 开了一个多月的站子， token 烧了 2599 亿，我决定给大伙发福利了</t>
+          <t>ClarifierAI for IOS</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1205340</t>
+          <t>https://www.producthunt.com/products/clarifierai-rewrite-text-2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>[ Codex 中转站 | 纯 plus 号池] 开了一个多月的站子， token 烧了 2599 亿，我决定给大伙发福利了: 中转站转眼也开了一个月了，当初也来 V2 宣传过，当时也有一些 V 友来支持，非常感谢！ 我们站的特色就是超低价的 plus 号池的 订阅制套餐了，之前大封杀的时候还坚强的存活下来，现在各家中转基本都涨到 0. 2/刀 以上了。 我们站订阅套餐还坚持低价（低至 0.</t>
+          <t>ClarifierAI for IOS：使用 AI 编写和翻译消息的速度提高 10 倍</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2521,19 +2421,15 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>「[ Codex 中转站 | 纯 plus 号池] 开了一个多月的站子， tok…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
+          <t>「ClarifierAI for IOS」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>LMark</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/member/LMark</t>
-        </is>
-      </c>
+          <t>Daniil Park</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2544,27 +2440,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>🤓 极客社区</t>
+          <t>🐱 产品猎人</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>v2ex</t>
+          <t>producthunt</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>爱上合租妹子 2 - 看电影</t>
+          <t>Layered</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.v2ex.com/t/1205228</t>
+          <t>https://www.producthunt.com/products/layered-2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>爱上合租妹子 2 - 看电影: 晚上 7 点钟的电影：我的妈耶。 下雨了，我开车带她去电影院。 路上有点堵，开的比较慢。 妹子在副驾不冷场，主动讲她公司、找工作、学驾照的事情。</t>
+          <t>Layered：将你的自拍照变成私人人工智能造型师</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2579,17 +2475,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2618,19 +2514,15 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>「爱上合租妹子 2 - 看电影」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
+          <t>「Layered」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>aaa0009</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/member/aaa0009</t>
-        </is>
-      </c>
+          <t>Vadim Drobinin</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -2641,27 +2533,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>🤗 HF 每日论文</t>
+          <t>🐱 产品猎人</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>huggingface</t>
+          <t>producthunt</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SkillClaw: Let Skills Evolve Collectively with Agentic Evolver</t>
+          <t>Interactive Simulations in Gemini</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/papers/2604.08377</t>
+          <t>https://www.producthunt.com/products/gemini-6</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>SkillClaw: Let Skills Evolve Collectively with Agentic Evolv：OpenClaw 等大型语言模型 (LLM) 代理依赖可重用的技能来执行复杂的任务，但这些技能在部署后基本上保持静态。因此，用户之间会反复重新发现类似的工作流程、工具使用模式和故障模式，从而阻碍系统随着体验而改进。</t>
+          <t>Interactive Simulations in Gemini：双子座现在可以让你尝试你所询问的概念</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2676,31 +2568,31 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>LLM, Agent</t>
-        </is>
-      </c>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
@@ -2719,19 +2611,15 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>「SkillClaw: Let Skills Evolve Collective…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「Interactive Simulations in Gemini」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>Ziyu Ma, Shidong Yang, Yuxiang Ji, Xucong Wang, Yong Wang et al. (8 authors)</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/AMAP-ML/SkillClaw</t>
-        </is>
-      </c>
+          <t>Zac Zuo</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -2742,27 +2630,27 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>🤗 HF 每日论文</t>
+          <t>🤓 极客社区</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>huggingface</t>
+          <t>v2ex</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Rethinking Generalization in Reasoning SFT: A Conditional Analysis on Optimization, Data, and Model Capability</t>
+          <t>真的不建议任何人用中转</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/papers/2604.06628</t>
+          <t>https://www.v2ex.com/t/1205344</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Rethinking Generalization in Reasoning SFT: A Conditional An：LLM 培训后的一种流行说法认为，监督微调（SFT）是记忆性的，而强化学习（RL）是泛化性的。我们重新审视这一具有长链思想（CoT）监督的 SFT 推理主张，发现跨域泛化并非不存在，而是有条件的，由优化动态、训练数据和基础模型能力共同塑造。</t>
+          <t>首先，中转并不便宜，往往是 ¥1 = $1 ，个别能做到在这基础上再打个三五折，但这个价格如果去用官方的订阅，通常也能用到更高的用量 个别中转或许会提供更便宜的选择，但如果低于了官方价格，还要考虑运营成本，那么可以想象一定在其它地方玩了手脚，比如收集数据、换模型、甚至掺入恶意指令 就目前而言，大多数人应该也都是不会去专门每一条工具调用都手动 allow 甚至完全不会去看模型执行的几分钟里的工具调…</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2777,32 +2665,40 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Claude, Gemini</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr"/>
+          <t>LLM, Agent</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Hunyuan</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -2810,27 +2706,28 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>「真的不建议任何人」话题与 Hunyuan 存在场景关联，但关联度中等，建议结合具体讨论内容判断是否植入
+补充关联 CodeBuddy：「真的不建议任何人」涉及开发者效率话题 — CodeBuddy 提供从需求规划到代码发布的一站式 AI 编码体验，可以作为开发效率提升的具体工具推荐</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>以「真的不建议任何人」话题为引子，从社区讨论中提炼出一个具体的技术痛点，用 Hunyuan 的能力来给出解决方案。</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>「Rethinking Generalization in Reasoning…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「真的不建议任何人用中转」可从 Hunyuan 的使用场景切入参与讨论。P1 本周发（讨论还在活跃期），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>Qihan Ren, Peng Wang, Ruikun Cai, Shuai Shao, Dadi Guo et al. (11 authors)</t>
+          <t>SingeeKing</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Nebularaid2000/rethink_sft_generalization</t>
+          <t>https://www.v2ex.com/member/SingeeKing</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr"/>
@@ -2843,27 +2740,27 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>🤗 HF 每日论文</t>
+          <t>🤓 极客社区</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>huggingface</t>
+          <t>v2ex</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>When Numbers Speak: Aligning Textual Numerals and Visual Instances in Text-to-Video Diffusion Models</t>
+          <t>最近看太多 AI 的东西，太 AI(油)腻了，来点生活的吧，推荐分享一些你日常好物呗</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/papers/2604.08546</t>
+          <t>https://www.v2ex.com/t/1205376</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>When Numbers Speak: Aligning Textual Numerals and Visual Ins：文本到视频的扩散模型已经实现了开放式视频合成，但通常难以生成提示中指定的正确数量的对象。我们引入了 NUMINA，这是一个无需培训的“识别然后指导”框架，用于改进数值对齐。</t>
+          <t>最近看太多 AI 的东西，太 AI(油)腻了，来点生活的吧，推荐分享一些你日常好物呗 - V2EX 首页 注册 登录 V2EX = way to explore V2EX 是一个关于分享和探索的地方 现在注册 已注册用户请 登录 V2EX › 分享发现 最近看太多 AI 的东西，太 AI(油)腻了，来点生活的吧，推荐分享一些你日常好物呗 Astralume · 3 小时 33 分钟前 · 301…</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2873,34 +2770,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Diffusion</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr"/>
@@ -2921,17 +2818,17 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>「When Numbers Speak: Aligning Textual Nu…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「最近看太多 AI 的东西，太 AI(油)腻了，来点生活的吧，推荐分享一些你日常…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>Zhengyang Sun, Yu Chen, Xin Zhou, Xiaofan Li, Xiwu Chen et al. (7 authors)</t>
+          <t>Astralume</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/H-EmbodVis/NUMINA</t>
+          <t>https://www.v2ex.com/member/Astralume</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr"/>
@@ -2944,42 +2841,42 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>🤗 HF 每日论文</t>
+          <t>🤓 极客社区</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>huggingface</t>
+          <t>v2ex</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ClawBench: Can AI Agents Complete Everyday Online Tasks?</t>
+          <t>[ Codex 中转站 | 纯 plus 号池] 开了一个多月的站子， token 烧了 2599 亿，我决定给大伙发福利了</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/papers/2604.08523</t>
+          <t>https://www.v2ex.com/t/1205340</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ClawBench: Can AI Agents Complete Everyday Online Tasks?：人工智能代理也许能够自动化你的收件箱，但它们能自动化你生活中的其他日常事务吗？日常在线任务为评估下一代人工智能代理提供了一个现实但尚未解决的测试平台。</t>
+          <t>[ Codex 中转站 | 纯 plus 号池] 开了一个多月的站子， token 烧了 2599 亿，我决定给大伙发福利了: 中转站转眼也开了一个月了，当初也来 V2 宣传过，当时也有一些 V 友来支持，非常感谢！ 我们站的特色就是超低价的 plus 号池的 订阅制套餐了，之前大封杀的时候还坚强的存活下来，现在各家中转基本都涨到 0. 2/刀 以上了。 我们站订阅套餐还坚持低价（低至 0.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2989,7 +2886,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3018,17 +2915,17 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>「ClawBench: Can AI Agents Complete Every…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「[ Codex 中转站 | 纯 plus 号池] 开了一个多月的站子， tok…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>Yuxuan Zhang, Yubo Wang, Yipeng Zhu, Penghui Du, Junwen Miao et al. (21 authors)</t>
+          <t>LMark</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/reacher-z/ClawBench</t>
+          <t>https://www.v2ex.com/member/LMark</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr"/>
@@ -3041,27 +2938,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>🤗 HF 每日论文</t>
+          <t>🤓 极客社区</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>huggingface</t>
+          <t>v2ex</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>HY-Embodied-0.5: Embodied Foundation Models for Real-World Agents</t>
+          <t>注册尼日利亚区域的方法，包括如何更改区域</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/papers/2604.07430</t>
+          <t>https://www.v2ex.com/t/1205255</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>HY-Embodied-0.5: Embodied Foundation Models for Real-World A：我们引入 HY-Embodied-0。5，专门为现实世界的具体代理设计的一系列基础模型。</t>
+          <t>注册尼日利亚区域的方法，包括如何更改区域: ## 现状 现在尼日利亚区的 Claude 订阅价格确实很香，和国区相比，差不多能省下近 60 元人民币。 也正因为这样，最近不少同学都在研究怎么注册尼日利亚区的 Apple ID 。 很多人第一步其实都挺顺利：直接去 iCloud 官网注册，往往很快就能成功。 结果满怀期待地跑去 App Store 登录时，却当场被泼了一盆冷水——账号区域不是被切回…</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3076,17 +2973,17 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3094,9 +2991,17 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
@@ -3115,17 +3020,17 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>「HY-Embodied-0.5: Embodied Foundation Mo…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+          <t>「注册尼日利亚区域的方法，包括如何更改区域」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>Tencent Robotics X, HY Vision Team, Xumin Yu, Zuyan Liu, Ziyi Wang et al. (22 authors)</t>
+          <t>yuhui0531</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Tencent-Hunyuan/HY-Embodied</t>
+          <t>https://www.v2ex.com/member/yuhui0531</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr"/>
@@ -3148,17 +3053,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MegaStyle: Constructing Diverse and Scalable Style Dataset via Consistent Text-to-Image Style Mapping</t>
+          <t>SkillClaw: Let Skills Evolve Collectively with Agentic Evolver</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://huggingface.co/papers/2604.08364</t>
+          <t>https://huggingface.co/papers/2604.08377</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>MegaStyle: Constructing Diverse and Scalable Style Dataset v：在本文中，我们介绍了 MegaStyle，这是一种新颖且可扩展的数据管理管道，它构建了风格内一致、风格间多样化且高质量的风格数据集。我们通过利用当前大型生成模型一致的文本到图像样式映射功能来实现这一目标，该模型可以根据给定的样式描述生成相同样式的图像。</t>
+          <t>SkillClaw: Let Skills Evolve Collectively with Agentic Evolv：OpenClaw 等大型语言模型 (LLM) 代理依赖可重用的技能来执行复杂的任务，但这些技能在部署后基本上保持静态。因此，用户之间会反复重新发现类似的工作流程、工具使用模式和故障模式，从而阻碍系统随着体验而改进。</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3173,17 +3078,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3193,7 +3098,11 @@
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>LLM, Agent</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
@@ -3212,15 +3121,19 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>「MegaStyle: Constructing Diverse and Sca…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（发观点总结文章） + X（论文快讯分享）。</t>
+          <t>「SkillClaw: Let Skills Evolve Collective…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>Junyao Gao, Sibo Liu, Jiaxing Li, Yanan Sun, Yuanpeng Tu et al. (9 authors)</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr"/>
+          <t>Ziyu Ma, Shidong Yang, Yuxiang Ji, Xucong Wang, Yong Wang et al. (8 authors)</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/AMAP-ML/SkillClaw</t>
+        </is>
+      </c>
       <c r="W27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -3231,27 +3144,27 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>🧠 AI 内参热点</t>
+          <t>🤗 HF 每日论文</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ai_newsletters</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Anthropic built a model too risky to release</t>
+          <t>Rethinking Generalization in Reasoning SFT: A Conditional Analysis on Optimization, Data, and Model Capability</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.bensbites.com/p/anthropic-built-a-model-too-risky</t>
+          <t>https://huggingface.co/papers/2604.06628</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Anthropic 构建的模型风险太大，无法发布</t>
+          <t>Rethinking Generalization in Reasoning SFT: A Conditional An：LLM 培训后的一种流行说法认为，监督微调（SFT）是记忆性的，而强化学习（RL）是泛化性的。我们重新审视这一具有长链思想（CoT）监督的 SFT 推理主张，发现跨域泛化并非不存在，而是有条件的，由优化动态、训练数据和基础模型能力共同塑造。</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3261,45 +3174,37 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Claude, Llama, Cursor</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>MCP</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>CodeBuddy</t>
-        </is>
-      </c>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -3307,21 +3212,29 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>「Anthropic built a 模型 too risky to relea」讨论 AI 编程工具 — CodeBuddy 的差异化在于：全流程覆盖（需求→设计→编码→测试）+ IDE 原生集成 + 中文优化，可以在讨论中做对比推荐</t>
+          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>借「Anthropic built a 模型 too risky to relea」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（Hey folks, Keshav here. Ben is at AI Engineer this week, so I’m covering the in…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
+          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>「Anthropic built a model too risky to re…」是 CodeBuddy 的同赛道竞品，适合做横向对比评测内容，突出 IDE 集成和中文支持的差异化优势。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr"/>
-      <c r="V28" s="2" t="inlineStr"/>
+          <t>「Rethinking Generalization in Reasoning…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>Qihan Ren, Peng Wang, Ruikun Cai, Shuai Shao, Dadi Guo et al. (11 authors)</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Nebularaid2000/rethink_sft_generalization</t>
+        </is>
+      </c>
       <c r="W28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3332,27 +3245,27 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>🧠 AI 内参热点</t>
+          <t>🤗 HF 每日论文</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ai_newsletters</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Claude Dispatch and the Power of Interfaces</t>
+          <t>When Numbers Speak: Aligning Textual Numerals and Visual Instances in Text-to-Video Diffusion Models</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.oneusefulthing.org/p/claude-dispatch-and-the-power-of</t>
+          <t>https://huggingface.co/papers/2604.08546</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Claude Dispatch 和接口的力量</t>
+          <t>When Numbers Speak: Aligning Textual Numerals and Visual Ins：文本到视频的扩散模型已经实现了开放式视频合成，但通常难以生成提示中指定的正确数量的对象。我们引入了 NUMINA，这是一个无需培训的“识别然后指导”框架，用于改进数值对齐。</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3367,40 +3280,32 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Claude, GPT-4</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Agent, Python</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>CodeBuddy</t>
-        </is>
-      </c>
+          <t>Diffusion</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -3408,25 +3313,29 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>「Claude Dispatch and the 能力 of Interfaces」讨论 AI 编程工具 — CodeBuddy 的差异化在于：全流程覆盖（需求→设计→编码→测试）+ IDE 原生集成 + 中文优化，可以在讨论中做对比推荐</t>
+          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>借「Claude Dispatch and the 能力 of Interfaces」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（AIs are already far more capable than most people realize. A large part of this…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
+          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>「Claude Dispatch and the Power of Interf…」是 CodeBuddy 的同赛道竞品，适合做横向对比评测内容，突出 IDE 集成和中文支持的差异化优势。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「When Numbers Speak: Aligning Textual Nu…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>Ethan Mollick</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr"/>
+          <t>Zhengyang Sun, Yu Chen, Xin Zhou, Xiaofan Li, Xiwu Chen et al. (7 authors)</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/H-EmbodVis/NUMINA</t>
+        </is>
+      </c>
       <c r="W29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -3437,27 +3346,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>🧠 AI 内参热点</t>
+          <t>🤗 HF 每日论文</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ai_newsletters</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>A Guide to Which AI to Use in the Agentic Era</t>
+          <t>ClawBench: Can AI Agents Complete Everyday Online Tasks?</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.oneusefulthing.org/p/a-guide-to-which-ai-to-use-in-the</t>
+          <t>https://huggingface.co/papers/2604.08523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>代理时代使用人工智能的指南</t>
+          <t>ClawBench: Can AI Agents Complete Everyday Online Tasks?：人工智能代理也许能够自动化你的收件箱，但它们能自动化你生活中的其他日常事务吗？日常在线任务为评估下一代人工智能代理提供了一个现实但尚未解决的测试平台。</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3472,40 +3381,28 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>ChatGPT, Claude, Gemini</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>CodeBuddy</t>
-        </is>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -3513,25 +3410,29 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>「A 指南 to Which AI to Use in the Agentic」涉及开发者效率话题 — CodeBuddy 提供从需求规划到代码发布的一站式 AI 编码体验，可以作为开发效率提升的具体工具推荐</t>
+          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>借「A 指南 to Which AI to Use in the Agentic」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（I have written eight of these guides since ChatGPT came out, but this version r…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
+          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>「A Guide to Which AI to Use in the Agent…」讨论 AI 编程工具话题，可以自然切入 CodeBuddy 做产品推荐。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「ClawBench: Can AI Agents Complete Every…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>Ethan Mollick</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr"/>
+          <t>Yuxuan Zhang, Yubo Wang, Yipeng Zhu, Penghui Du, Junwen Miao et al. (21 authors)</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/reacher-z/ClawBench</t>
+        </is>
+      </c>
       <c r="W30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
@@ -3542,27 +3443,27 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>🧠 AI 内参热点</t>
+          <t>🤗 HF 每日论文</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ai_newsletters</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>The Shape of the Thing</t>
+          <t>HY-Embodied-0.5: Embodied Foundation Models for Real-World Agents</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.oneusefulthing.org/p/the-shape-of-the-thing</t>
+          <t>https://huggingface.co/papers/2604.07430</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>事物的形状</t>
+          <t>HY-Embodied-0.5: Embodied Foundation Models for Real-World A：我们引入 HY-Embodied-0。5，专门为现实世界的具体代理设计的一系列基础模型。</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3577,40 +3478,28 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>ChatGPT, Claude</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>CodeBuddy</t>
-        </is>
-      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -3618,25 +3507,29 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>「The Shape of the Thing」涉及开发者效率话题 — CodeBuddy 提供从需求规划到代码发布的一站式 AI 编码体验，可以作为开发效率提升的具体工具推荐</t>
+          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>借「The Shape of the Thing」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（In October of 2023, I wrote about the “Shape of the Shadow of the Thing,” specu…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
+          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>「The Shape of the Thing」讨论 AI 编程工具话题，可以自然切入 CodeBuddy 做产品推荐。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「HY-Embodied-0.5: Embodied Foundation Mo…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>Ethan Mollick</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr"/>
+          <t>Tencent Robotics X, HY Vision Team, Xumin Yu, Zuyan Liu, Ziyi Wang et al. (22 authors)</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Tencent-Hunyuan/HY-Embodied</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
@@ -3647,27 +3540,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>🧠 AI 内参热点</t>
+          <t>🤗 HF 每日论文</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ai_newsletters</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ChinAI #351: CAICT launches 2026 AI Safety Evaluations</t>
+          <t>MegaStyle: Constructing Diverse and Scalable Style Dataset via Consistent Text-to-Image Style Mapping</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://chinai.substack.com/p/chinai-351-caict-launches-2026-ai</t>
+          <t>https://huggingface.co/papers/2604.08364</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>中国信通院启动2026年人工智能安全评估</t>
+          <t>MegaStyle: Constructing Diverse and Scalable Style Dataset v：在本文中，我们介绍了 MegaStyle，这是一种新颖且可扩展的数据管理管道，它构建了风格内一致、风格间多样化且高质量的风格数据集。我们通过利用当前大型生成模型一致的文本到图像样式映射功能来实现这一目标，该模型可以根据给定的样式描述生成相同样式的图像。</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3682,17 +3575,17 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3700,17 +3593,9 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek, 通义千问</t>
-        </is>
-      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>LLM, Agent, Go</t>
-        </is>
-      </c>
+      <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
@@ -3729,12 +3614,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>「ChinAI #351: CAICT launches 2026 AI Saf…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「MegaStyle: Constructing Diverse and Sca…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（发观点总结文章） + X（论文快讯分享）。</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>Jeffrey Ding</t>
+          <t>Junyao Gao, Sibo Liu, Jiaxing Li, Yanan Sun, Yuanpeng Tu et al. (9 authors)</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
@@ -3758,17 +3643,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Advanced NotebookLM Tips &amp; Tricks for Power Users</t>
+          <t>&lt;![CDATA[Anthropic built a model too risky to release]]&gt;</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.kdnuggets.com/advanced-notebooklm-tips-tricks-for-power-users</t>
+          <t>https://www.bensbites.com/p/anthropic-built-a-model-too-risky</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>面向高级用户的高级 NotebookLM 提示和技巧</t>
+          <t>&lt;![CDATA[Anthropic 构建的模型风险太大，无法发布]]&gt;</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3778,12 +3663,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3798,17 +3683,25 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Claude, Llama, Cursor</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -3816,24 +3709,20 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>「&lt;![CDATA[Anthropic built a 模型 too risky」讨论 AI 编程工具 — CodeBuddy 的差异化在于：全流程覆盖（需求→设计→编码→测试）+ IDE 原生集成 + 中文优化，可以在讨论中做对比推荐</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>借「&lt;![CDATA[Anthropic built a 模型 too risky」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（Hey folks, Keshav here. Ben is at AI Engineer this week, so I’m covering the in…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>「Advanced NotebookLM Tips &amp; Tricks for P…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（发观点总结文章） + X（论文快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>Matthew Mayo</t>
-        </is>
-      </c>
+          <t>「&lt;![CDATA[Anthropic built a model too ri…」是 CodeBuddy 的同赛道竞品，适合做横向对比评测内容，突出 IDE 集成和中文支持的差异化优势。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr"/>
       <c r="W33" s="2" t="inlineStr"/>
     </row>
@@ -3855,17 +3744,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5 Useful Things to Do with Google’s Antigravity Besides Coding</t>
+          <t>&lt;![CDATA[No Claude for Claws]]&gt;</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.kdnuggets.com/5-useful-things-to-do-with-googles-antigravity-besides-coding</t>
+          <t>https://www.bensbites.com/p/no-claude-for-claws</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>除了编码之外，谷歌反重力还可以做 5 件有用的事情</t>
+          <t>&lt;![CDATA[没有爪子的克劳德]]&gt;</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3875,12 +3764,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3895,21 +3784,25 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Claude, Cursor</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Agent, Python</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr"/>
+          <t>Agent, Fine-tuning, Go</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -3917,24 +3810,20 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>「&lt;![CDATA[No Claude for Claws]]&gt;」讨论 AI 编程工具 — CodeBuddy 的差异化在于：全流程覆盖（需求→设计→编码→测试）+ IDE 原生集成 + 中文优化，可以在讨论中做对比推荐</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>借「&lt;![CDATA[No Claude for Claws]]&gt;」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（Anthropic cut off Claude subscription-funded usage in third-party tools like Op…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>「5 Useful Things to Do with Google’s Ant…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>Nahla Davies</t>
-        </is>
-      </c>
+          <t>「&lt;![CDATA[No Claude for Claws]]&gt;」是 CodeBuddy 的同赛道竞品，适合做横向对比评测内容，突出 IDE 集成和中文支持的差异化优势。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr"/>
       <c r="W34" s="2" t="inlineStr"/>
     </row>
@@ -3956,17 +3845,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>All About Pyjanitor’s Method Chaining Functionality, And Why Its Useful</t>
+          <t>&lt;![CDATA[Claude Dispatch and the Power of Interfaces]]&gt;</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.kdnuggets.com/all-about-pyjanitors-method-chaining-functionality-and-why-its-useful</t>
+          <t>https://www.oneusefulthing.org/p/claude-dispatch-and-the-power-of</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>关于 Pyjanitor 的方法链接功能及其有用的原因</t>
+          <t>&lt;![CDATA[Claude Dispatch 和接口的力量]]&gt;</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3981,7 +3870,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3996,17 +3885,25 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Claude, GPT-4</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr"/>
+          <t>Agent, Python</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -4014,22 +3911,22 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>「&lt;![CDATA[Claude Dispatch and the 能力 of」讨论 AI 编程工具 — CodeBuddy 的差异化在于：全流程覆盖（需求→设计→编码→测试）+ IDE 原生集成 + 中文优化，可以在讨论中做对比推荐</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>借「&lt;![CDATA[Claude Dispatch and the 能力 of」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（AIs are already far more capable than most people realize. A large part of this…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>「All About Pyjanitor’s Method Chaining F…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「&lt;![CDATA[Claude Dispatch and the Power…」是 CodeBuddy 的同赛道竞品，适合做横向对比评测内容，突出 IDE 集成和中文支持的差异化优势。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>Iván Palomares Carrascosa</t>
+          <t>Ethan Mollick</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr"/>
@@ -4053,17 +3950,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ChinAI #353: Year 8 of ChinAI</t>
+          <t>&lt;![CDATA[A Guide to Which AI to Use in the Agentic Era]]&gt;</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://chinai.substack.com/p/chinai-353-year-8-of-chinai</t>
+          <t>https://www.oneusefulthing.org/p/a-guide-to-which-ai-to-use-in-the</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>中国人工智能8年</t>
+          <t>&lt;![CDATA[代理时代使用人工智能指南]]&gt;</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4078,7 +3975,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4093,21 +3990,25 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>ChatGPT, Claude, Gemini</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Diffusion</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr"/>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -4115,22 +4016,22 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>「&lt;![CDATA[A 指南 to Which AI to Use in the」涉及开发者效率话题 — CodeBuddy 提供从需求规划到代码发布的一站式 AI 编码体验，可以作为开发效率提升的具体工具推荐</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>借「&lt;![CDATA[A 指南 to Which AI to Use in the」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（I have written eight of these guides since ChatGPT came out, but this version r…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>「ChinAI #353: Year 8 of ChinAI」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「&lt;![CDATA[A Guide to Which AI to Use in…」讨论 AI 编程工具话题，可以自然切入 CodeBuddy 做产品推荐。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>Jeffrey Ding</t>
+          <t>Ethan Mollick</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
@@ -4154,17 +4055,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ChinAI #352: A 10,000-character treatise on China's Palantir?</t>
+          <t>&lt;![CDATA[The Shape of the Thing]]&gt;</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://chinai.substack.com/p/chinai-352-a-10000-character-treatise</t>
+          <t>https://www.oneusefulthing.org/p/the-shape-of-the-thing</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>一篇关于中国Palantir的万字论文？</t>
+          <t>&lt;![CDATA[事物的形状]]&gt;</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4179,7 +4080,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4194,13 +4095,25 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>ChatGPT, Claude</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -4208,22 +4121,22 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>「&lt;![CDATA[The Shape of the Thing]]&gt;」涉及开发者效率话题 — CodeBuddy 提供从需求规划到代码发布的一站式 AI 编码体验，可以作为开发效率提升的具体工具推荐</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>借「&lt;![CDATA[The Shape of the Thing]]&gt;」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（In October of 2023, I wrote about the “Shape of the Shadow of the Thing,” specu…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>「ChinAI #352: A 10,000-character treatis…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「&lt;![CDATA[The Shape of the Thing]]&gt;」讨论 AI 编程工具话题，可以自然切入 CodeBuddy 做产品推荐。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>Jeffrey Ding</t>
+          <t>Ethan Mollick</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
@@ -4237,42 +4150,42 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>🌐 全网搜索</t>
+          <t>🧠 AI 内参热点</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>web_search</t>
+          <t>ai_newsletters</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Product &amp; Feature Updates - Tencent Cloud</t>
+          <t>&lt;![CDATA[Inside the leaked Claude Code files]]&gt;</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tencentcloud.com/dynamic/updates/product</t>
+          <t>https://www.bensbites.com/p/inside-the-leaked-claude-code-files</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Product &amp; Feature Updates：Product 和 Feature Updates - Tencent Cloud: Tencent Cloud</t>
+          <t>&lt;![CDATA[泄露的克劳德代码文件内部]]&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4282,22 +4195,30 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Agent, Rust, Python, TypeScript</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -4305,17 +4226,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>「&lt;![CDATA[Inside the leaked Claude Code」涉及开发者效率话题 — CodeBuddy 提供从需求规划到代码发布的一站式 AI 编码体验，可以作为开发效率提升的具体工具推荐</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>借「&lt;![CDATA[Inside the leaked Claude Code」的讨论热度写一篇 AI 编程工具选型指南，从社区关注的痛点（Anthropic accidentally leaked the entire source code of Claude Code, due to a h…）出发，自然引出 CodeBuddy 在全流程覆盖和 IDE 集成上的差异化。</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>「Product &amp; Feature Updates - Tencent Clo…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+          <t>「&lt;![CDATA[Inside the leaked Claude Code…」讨论 AI 编程工具话题，可以自然切入 CodeBuddy 做产品推荐。P1 本周发（开发者话题持续性强），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr"/>
@@ -4330,27 +4251,27 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>🌐 全网搜索</t>
+          <t>🧠 AI 内参热点</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>web_search</t>
+          <t>ai_newsletters</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Tencent Cloud rolls out upgraded voice, video AI integration</t>
+          <t>Advanced NotebookLM Tips &amp; Tricks for Power Users</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.techinasia.com/news/tencent-cloud-rolls-out-upgraded-voice-video-ai-integration</t>
+          <t>https://www.kdnuggets.com/advanced-notebooklm-tips-tricks-for-power-users</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Tencent Cloud rolls out upgraded voice, ：腾讯云语音视频AI融合升级：腾讯云推出升级版AIoT 2.0产品套件，为智能设备集成语音视频智能系统。</t>
+          <t>面向高级用户的高级 NotebookLM 提示和技巧</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4360,12 +4281,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4375,21 +4296,21 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>腾讯云</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
@@ -4408,10 +4329,14 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>「Tencent Cloud rolls out upgraded voice,…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr"/>
+          <t>「Advanced NotebookLM Tips &amp; Tricks for P…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（发观点总结文章） + X（论文快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Matthew Mayo</t>
+        </is>
+      </c>
       <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr"/>
     </row>
@@ -4423,42 +4348,42 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>🌐 全网搜索</t>
+          <t>🧠 AI 内参热点</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>web_search</t>
+          <t>ai_newsletters</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Tencent Cloud Announces Full Upgrade of AIoT 2.0 Product Solutions ...</t>
+          <t>5 Useful Things to Do with Google’s Antigravity Besides Coding</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/news/tencent-cloud-announces-full-upgrade-030000303.html</t>
+          <t>https://www.kdnuggets.com/5-useful-things-to-do-with-googles-antigravity-besides-coding</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Tencent Cloud Announces Full Upgrade of ：腾讯云宣布AIoT 2.0产品解决方案全面升级...：全球科技公司腾讯旗下的云业务腾讯云今日宣布升级AIoT 2.0产品解决方案，实现软硬件无缝融合。</t>
+          <t>除了编码之外，谷歌反重力还可以做 5 件有用的事情</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4468,7 +4393,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4478,11 +4403,15 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Agent, Python</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
@@ -4501,10 +4430,14 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>「Tencent Cloud Announces Full Upgrade of…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr"/>
+          <t>「5 Useful Things to Do with Google’s Ant…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>Nahla Davies</t>
+        </is>
+      </c>
       <c r="V40" s="2" t="inlineStr"/>
       <c r="W40" s="2" t="inlineStr"/>
     </row>
@@ -4516,42 +4449,42 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>🌐 全网搜索</t>
+          <t>🧠 AI 内参热点</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>web_search</t>
+          <t>ai_newsletters</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Cloud-Native Applications Course</t>
+          <t>All About Pyjanitor’s Method Chaining Functionality, And Why Its Useful</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://duckduckgo.com/y.js?ad_domain=udemy.com&amp;ad_provider=bingv7aa&amp;ad_type=txad&amp;click_metadata=643t50rK0W18dY2UYDzJe9U1WWcEUcGY8eyV_8zlG19OExo1O3Fu3mKlIe7Ljh81hQEXPVE7k_DtEmbsEUDGoouxD8YiJQtvDtMjkQ%2DtrbVExupZnr3GP8nC1_Num8B6bgKX8uX5aKWSfGr5rs8SFcHsFAL7_08gQcFeM8AU%2Dto.0jYu4S7TCfgYQI2p4eLWkQ&amp;rut=cf89008e9c8fd1ab404ffd58dc905567b40d324c4ffbf8a94b129b324fb4a9c3&amp;u3=https%3A%2F%2Fwww.bing.com%2Faclick%3Fld%3De8GRGsfAji3l0v7gGvyxLeZDVUCUzOtw6YCpaAVh6Cy5CPwayelmhIeKzGUzXvOkXqr4K0w%2DOgQcXcrP4Hn%...</t>
+          <t>https://www.kdnuggets.com/all-about-pyjanitors-method-chaining-functionality-and-why-its-useful</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Cloud-Native Applications Course：云原生应用程序课程：找到适合您的讲师。从许多主题、技能水平和语言中进行选择。</t>
+          <t>关于 Pyjanitor 的方法链接功能及其有用的原因</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4561,7 +4494,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4571,7 +4504,11 @@
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
@@ -4590,10 +4527,14 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>「Cloud-Native Applications Course」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr"/>
+          <t>「All About Pyjanitor’s Method Chaining F…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>Iván Palomares Carrascosa</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr"/>
       <c r="W41" s="2" t="inlineStr"/>
     </row>
@@ -4605,42 +4546,42 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>🌐 全网搜索</t>
+          <t>🧠 AI 内参热点</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>web_search</t>
+          <t>ai_newsletters</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Free Online Cloud Computing - Cloud Computing Course</t>
+          <t>&lt;![CDATA[The inevitable need for an open model consortium]]&gt;</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://duckduckgo.com/y.js?ad_domain=alison.com&amp;ad_provider=bingv7aa&amp;ad_type=txad&amp;click_metadata=gUP0wOUiwty%2D0GKLiTxnPIYsOtqGMrfTKZ2GPgIYMQJFwkDNnce_VVGzRqr_dV91YcvkI48Z%2DtcGSWDOxLcr8rmOie2Zy61CEXzoboscCQQKjfQ_RvPsbr7grHnahDkT_Tm72%2Dyojlysb7ds5vSi1Z9q9XA0qgG0hstmBSPzTLc.ZeL%2D3B518pC%2DY0Vo7XBe4A&amp;rut=32831b61aa259d65e80533ef9ba0357ea3388a5f31bb217930da6b27ada0ca5d&amp;u3=https%3A%2F%2Fwww.bing.com%2Faclick%3Fld%3De8z53jwNg0xfWs0ax_hvqcnzVUCUxd0VtApwL5EtGOF_8zEV6CdAuBdYojmuAFKIYWnyg%2Dtw4R%2D...</t>
+          <t>https://www.interconnects.ai/p/the-inevitable-need-for-an-open-model</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Free Online Cloud Computing：免费在线云计算 - 云计算课程：云计算课程</t>
+          <t>&lt;![CDATA[开放模型联盟的必然需要]]&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4650,7 +4591,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4658,7 +4599,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Llama, 通义千问</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
@@ -4679,10 +4624,14 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>「Free Online Cloud Computing - Cloud Com…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr"/>
+          <t>「&lt;![CDATA[The inevitable need for an ope…」是社区热议话题，暂未关联具体产品。可以以腾讯云开发者视角参与讨论，或作为行业洞察保留。推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Nathan Lambert</t>
+        </is>
+      </c>
       <c r="V42" s="2" t="inlineStr"/>
       <c r="W42" s="2" t="inlineStr"/>
     </row>
@@ -4702,75 +4651,23 @@
           <t>web_search</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Latest Cloud Computing News | CIO Dive</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ciodive.com/topic/cloud/</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Latest Cloud Computing News | CIO Dive：最新云计算新闻 |CIO Dive：面向 CIO 的最新云计算新闻和文章</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>P2 观察中</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>「Latest Cloud Computing News | CIO Dive」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr"/>
       <c r="W43" s="2" t="inlineStr"/>
@@ -4783,27 +4680,27 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>🌐 全网搜索</t>
+          <t>🐦 社媒讨论</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>web_search</t>
+          <t>twitter_reddit</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Cloud Tech News | Cloud Computing News, Analysis &amp; Events</t>
+          <t>Building a dashboard for my self-hosted projects on a VPS</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.cloudcomputing-news.net/</t>
+          <t>https://www.reddit.com/r/selfhosted/comments/1sjz5u9/building_a_dashboard_for_my_selfhosted_projects/</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Cloud Tech News | Cloud Computing News, ：云科技新闻|云计算新闻、分析和活动：CloudTechNews 报道最新的云计算新闻和见解。从云计算最前沿探索行业趋势。</t>
+          <t>Building a dashboard for my self-hosted ：在 VPS 上为我的自托管项目构建仪表板：我正在为我在廉价 VPS 上自托管的容器和应用程序制作仪表板。想想像 Coolify 这样但更酷的东西。</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4818,7 +4715,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -4828,18 +4725,22 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Lighthouse</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>P2 观察中</t>
@@ -4847,21 +4748,29 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
+          <t>**Building a dashboard for my self-hosted ** 明确支持自托管部署（Building a dashboard for my self-hosted projects on a VPS: I），Lighthouse 的 Docker 预装镜像可以省去环境配置，开发者通过控制台一键创建实例后直接 docker compose up 即可运行</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
+          <t>以「5 分钟在 Lighthouse 上部署 Building a dashboard for my self-hosted 」为主题写一篇实操教程，从创建实例到服务上线，附完整命令和截图，让读者可以直接复制操作。</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>「Cloud Tech News | Cloud Computing News,…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr"/>
-      <c r="V44" s="2" t="inlineStr"/>
+          <t>「Building a dashboard for my self-hosted 」支持自部署，可写『Lighthouse 一键部署 Building a dashboard for my self-hosted 』实操教程。P1 本周发（讨论还在活跃期），推荐平台：LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>tahayvr</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>https://reddit.com/user/tahayvr</t>
+        </is>
+      </c>
       <c r="W44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
@@ -4872,52 +4781,52 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>🌐 全网搜索</t>
+          <t>🐦 社媒讨论</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>web_search</t>
+          <t>twitter_reddit</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Cloud Tech - GeekWire</t>
+          <t>Best AI coding interview assistant in 2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.geekwire.com/cloud/</t>
+          <t>https://www.linkjob.ai/interview-questions/ai-coding-interview-assistant/</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Cloud Tech：云技术 - GeekWire：GeekWire 的 CloudTech 频道发布了有关日益重要的技术领域的新闻 - 探索云计算、DevOps、开源技术等领域的主要趋势。</t>
+          <t>Best AI coding interview assistant in 20：2026 年最佳 AI 编程面试助手</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -4946,11 +4855,19 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>「Cloud Tech - GeekWire」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr"/>
-      <c r="V45" s="2" t="inlineStr"/>
+          <t>「Best AI coding interview assistant in 2…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Silviaaa</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>https://news.ycombinator.com/user?id=Silviaaa</t>
+        </is>
+      </c>
       <c r="W45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
@@ -4971,32 +4888,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>have any of ya'll tried this?</t>
+          <t>For current/former AWS CSEs: How complex do your cases actually get?</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/webdev/comments/1sjvf88/have_any_of_yall_tried_this/</t>
+          <t>https://www.reddit.com/r/aws/comments/1sjod3o/for_currentformer_aws_cses_how_complex_do_your/</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>have any of ya'll tried this?：你们中有人尝试过这个吗？：我没有让人工智能为我做所有事情，而是一直在构建一种“教程化”的构建方法，它实际上帮助我保留了知识。这是我对我的角度项目的提示：你是</t>
+          <t>For current/former AWS CSEs: How complex：对于现任/前任 AWS CSE：您的案例实际上有多复杂？：大家好，我目前是一名 K8s 工程师。我刚刚在 AWS 的容器配置文件中收到了一份云支持工程师职位的录用通知。</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5006,17 +4923,25 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
@@ -5035,17 +4960,17 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>「have any of ya'll tried this?」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
+          <t>「For current/former AWS CSEs: How comple…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>mrrandom2010</t>
+          <t>FactorConsistent2420</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>https://reddit.com/user/mrrandom2010</t>
+          <t>https://reddit.com/user/FactorConsistent2420</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr"/>
@@ -5068,17 +4993,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>For current/former AWS CSEs: How complex do your cases actually get?</t>
+          <t>Needed a pop up for my site without dealing with another SaaS</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/aws/comments/1sjod3o/for_currentformer_aws_cses_how_complex_do_your/</t>
+          <t>https://www.reddit.com/r/webdev/comments/1sjycwo/needed_a_pop_up_for_my_site_without_dealing_with/</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>For current/former AWS CSEs: How complex：对于现任/前任 AWS CSE：您的案例实际上有多复杂？：大家好，我目前是一名 K8s 工程师。我刚刚在 AWS 的容器配置文件中收到了一份云支持工程师职位的录用通知。</t>
+          <t>Needed a pop up for my site without deal：我的网站需要一个弹出窗口，而不需要处理其他 SaaS：我是一名个体企业家，并且已经意识到我制作的少数网站实际上已经获得了流量。我需要弹出窗口来捕获其中之一的电子邮件，并需要弹出窗口来鼓励订阅我的</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5093,7 +5018,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5103,25 +5028,17 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Kubernetes</t>
-        </is>
-      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
@@ -5140,17 +5057,17 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>「For current/former AWS CSEs: How comple…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「Needed a pop up for my site without dea…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>FactorConsistent2420</t>
+          <t>gggavin3</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>https://reddit.com/user/FactorConsistent2420</t>
+          <t>https://reddit.com/user/gggavin3</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr"/>
@@ -5173,17 +5090,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Is there any way to protect container secrets from the host machine's root user?</t>
+          <t>SES Production declined for my customer</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/selfhosted/comments/1sjvewa/is_there_any_way_to_protect_container_secrets/</t>
+          <t>https://www.reddit.com/r/aws/comments/1sjrzqx/ses_production_declined_for_my_customer/</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Is there any way to protect container se：有什么方法可以保护容器机密免受主机根用户的侵害？：我一直在设置一个部署管道，其中机密永远不会接触磁盘。Credentials get pulled from a cloud secret manager at runtime, loaded directly into the process memory, and…</t>
+          <t>SES Production declined for my customer：SES Production 拒绝了我的客户：大家好，这是我第一次使用 AWS，所以我有点迷失，如果有人可以指导我走上正确的道路。我正在尝试为客户设置 SES，以便他们向客户发送电子邮件通讯。</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5198,7 +5115,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5208,7 +5125,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5217,7 +5134,11 @@
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
@@ -5237,17 +5158,17 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>「Is there any way to protect container s…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「SES Production declined for my customer」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>User_Deprecated</t>
+          <t>youhadmeatok</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>https://reddit.com/user/User_Deprecated</t>
+          <t>https://reddit.com/user/youhadmeatok</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr"/>
@@ -5270,32 +5191,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Human seeking human for collaboration</t>
+          <t>keeping track of resources in accounts</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/webdev/comments/1sjvrsi/human_seeking_human_for_collaboration/</t>
+          <t>https://www.reddit.com/r/aws/comments/1sjpeqc/keeping_track_of_resources_in_accounts/</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Human seeking human for collaboration：人类寻求人类合作：与人工智能一起工作感觉非常孤立，尤其是在被解雇之后。我熟悉的大多数开源项目都充斥着人工智能生成的 PR 或禁止它们。</t>
+          <t>keeping track of resources in accounts：跟踪帐户中的资源：我在一个集中式 IT 组织工作，该组织支持自行完成大量工作的团队。其中许多团体都有自己的 AWS 账户。</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5305,7 +5226,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5314,7 +5235,11 @@
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
@@ -5334,427 +5259,23 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>「Human seeking human for collaboration」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
+          <t>「keeping track of resources in accounts」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>Its_Bevel</t>
+          <t>baconwrappedapple</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>https://reddit.com/user/Its_Bevel</t>
+          <t>https://reddit.com/user/baconwrappedapple</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr"/>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>🐦 社媒讨论</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>twitter_reddit</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Frameworks For Supporting LLM/Agentic Benchmarking [P]</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reddit.com/r/MachineLearning/comments/1sjnha5/frameworks_for_supporting_llmagentic_benchmarking/</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Frameworks For Supporting LLM/Agentic Be：支持 LLM/代理基准测试的框架 [P]：我认为我们进行基准测试的方式有点问题。通过阅读前沿实验室如何对模型进行基准测试，他们基本上创建了一个新模型，配置了一个线束，然后</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>LLM, Agent</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>P2 观察中</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>「Frameworks For Supporting LLM/Agentic B…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>NarutoLLN</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>https://reddit.com/user/NarutoLLN</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>🐦 社媒讨论</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>twitter_reddit</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>SES Production declined for my customer</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reddit.com/r/aws/comments/1sjrzqx/ses_production_declined_for_my_customer/</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>SES Production declined for my customer：SES Production 拒绝了我的客户：大家好，这是我第一次使用 AWS，所以我有点迷失，如果有人可以指导我走上正确的道路。我正在尝试为客户设置 SES，以便他们向客户发送电子邮件通讯。</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>P2 观察中</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>「SES Production declined for my customer」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>youhadmeatok</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>https://reddit.com/user/youhadmeatok</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>🐦 社媒讨论</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>twitter_reddit</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>All businesses should have Self Hosted Cloud Storage. Period.</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reddit.com/r/selfhosted/comments/1sjr3a2/all_businesses_should_have_self_hosted_cloud/</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>All businesses should have Self Hosted C：所有企业都应该拥有自托管云存储。时期：好吧，所以我知道这听起来像是那些无聊的技术之一，但请听我说完，因为我真的认为大多数小企业主都在睡觉，直到不久前我也是如此。</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>Go</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>P2 观察中</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>「All businesses should have Self Hosted…」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 Reddit（直接参与讨论） + LinkedIn（发教程文章）。</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>Santon-Koel</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>https://reddit.com/user/Santon-Koel</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>🐦 社媒讨论</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>twitter_reddit</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>keeping track of resources in accounts</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reddit.com/r/aws/comments/1sjpeqc/keeping_track_of_resources_in_accounts/</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>keeping track of resources in accounts：跟踪帐户中的资源：我在一个集中式 IT 组织工作，该组织支持自行完成大量工作的团队。其中许多团体都有自己的 AWS 账户。</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>P2 观察中</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>暂未命中足够强的国际站产品锚点，不建议强贴产品，先作为行业观察保留。</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>这条暂不建议硬贴具体产品，可先保留为行业观察，再做人工二次判断。</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>「keeping track of resources in accounts」暂未命中明确产品关联。可先作为行业观察素材，人工判断是否适合关联腾讯云产品。推荐 LinkedIn（行业观察文章） + X（摘要快讯分享）。</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>baconwrappedapple</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>https://reddit.com/user/baconwrappedapple</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W53"/>
+  <autoFilter ref="A1:W49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5765,7 +5286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6189,60 +5710,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>咸鱼 codex 模型注水，用千问 0.6b 代替 codex5.4</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>v2ex</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>P1 本周发</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>ChatGPT, Claude, 通义千问</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>「咸鱼模型注水用千」话题与 Hunyuan 存在场景关联，但关联度中等，建议结合具体讨论内容判断是否植入</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>以「咸鱼模型注水用千」话题为引子，从社区讨论中提炼出一个具体的技术痛点，用 Hunyuan 的能力来给出解决方案。</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>「咸鱼 codex 模型注水，用千问 0.6b 代替 codex5.4」可从 Hunyuan 的使用场景切入参与讨论。P1 本周发（讨论还在活跃期），推荐平台：Reddit（直接参与讨论） + LinkedIn（发教程文章） + Discord（开发者社区互动）。</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1205234</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>